--- a/data/grant_es.xlsx
+++ b/data/grant_es.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Documents\GitHub\Mile_CV\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E499907-CF2C-4EB6-AAF1-539A72543EB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95280B3B-6ACD-4F1E-AFF8-94AC3479C6DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="47">
   <si>
     <t>what</t>
   </si>
@@ -140,6 +140,28 @@
   </si>
   <si>
     <t>Proyecto: Diferencias en el patrón de rastreo ocular hacia estímulos sexualmente preferidos en hombres condenados por delitos sexuales y población en general</t>
+  </si>
+  <si>
+    <t>\href{https://sshrc-crsh.canada.ca/en/funding/opportunities/partnership-engage-grants.aspx}{Partnership Engage Grants}, 2024</t>
+  </si>
+  <si>
+    <t>Dic. 2024 - Dic. 2025</t>
+  </si>
+  <si>
+    <t>\href{https://sshrc-crsh.canada.ca/en.aspx}{Social Sciences and Humanities Research Council}</t>
+  </si>
+  <si>
+    <t>Halifax, Canada</t>
+  </si>
+  <si>
+    <t>CAD\$25.000</t>
+  </si>
+  <si>
+    <t>Proyecto: Alianza para la prevención de la explotación sexual de niños, niñas y adolescentes en el sector de los viajes y el turismo en
+Colombia</t>
+  </si>
+  <si>
+    <t>Role: Coinvestigadora</t>
   </si>
 </sst>
 </file>
@@ -989,7 +1011,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E21"/>
+  <dimension ref="A1:E24"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="75" bestFit="1" customWidth="1"/>
@@ -1016,21 +1038,21 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" ht="72" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>9</v>
+        <v>42</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>5</v>
+        <v>43</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
@@ -1039,7 +1061,7 @@
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
       <c r="E3" s="1" t="s">
-        <v>22</v>
+        <v>46</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
@@ -1048,24 +1070,24 @@
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
       <c r="E4" s="2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>28</v>
+        <v>5</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
@@ -1073,60 +1095,60 @@
       <c r="B6" s="1"/>
       <c r="C6" s="1"/>
       <c r="D6" s="1"/>
-      <c r="E6" s="2" t="s">
+      <c r="E6" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7" s="1"/>
+      <c r="B7" s="1"/>
+      <c r="C7" s="1"/>
+      <c r="D7" s="1"/>
+      <c r="E7" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A8" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9" s="1"/>
+      <c r="B9" s="1"/>
+      <c r="C9" s="1"/>
+      <c r="D9" s="1"/>
+      <c r="E9" s="2" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A7" s="1" t="s">
+    <row r="10" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A10" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="B10" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="C10" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D7" s="1" t="s">
+      <c r="D10" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="E7" s="1" t="s">
+      <c r="E10" s="1" t="s">
         <v>26</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A8" s="1"/>
-      <c r="B8" s="1"/>
-      <c r="C8" s="1"/>
-      <c r="D8" s="1"/>
-      <c r="E8" s="2" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A9" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A10" s="1"/>
-      <c r="B10" s="1"/>
-      <c r="C10" s="1"/>
-      <c r="D10" s="1"/>
-      <c r="E10" s="1" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
@@ -1135,24 +1157,24 @@
       <c r="C11" s="1"/>
       <c r="D11" s="1"/>
       <c r="E11" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>5</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>8</v>
+        <v>38</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
@@ -1161,7 +1183,7 @@
       <c r="C13" s="1"/>
       <c r="D13" s="1"/>
       <c r="E13" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
@@ -1170,15 +1192,15 @@
       <c r="C14" s="1"/>
       <c r="D14" s="1"/>
       <c r="E14" s="2" t="s">
-        <v>11</v>
+        <v>24</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>9</v>
@@ -1186,8 +1208,8 @@
       <c r="D15" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="E15" s="2" t="s">
-        <v>39</v>
+      <c r="E15" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
@@ -1196,7 +1218,7 @@
       <c r="C16" s="1"/>
       <c r="D16" s="1"/>
       <c r="E16" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.3">
@@ -1205,24 +1227,24 @@
       <c r="C17" s="1"/>
       <c r="D17" s="1"/>
       <c r="E17" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" ht="72" x14ac:dyDescent="0.3">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E18" s="1" t="s">
-        <v>19</v>
+        <v>5</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.3">
@@ -1240,15 +1262,50 @@
       <c r="C20" s="1"/>
       <c r="D20" s="1"/>
       <c r="E20" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" ht="72" x14ac:dyDescent="0.3">
+      <c r="A21" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A22" s="1"/>
+      <c r="B22" s="1"/>
+      <c r="C22" s="1"/>
+      <c r="D22" s="1"/>
+      <c r="E22" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A23" s="1"/>
+      <c r="B23" s="1"/>
+      <c r="C23" s="1"/>
+      <c r="D23" s="1"/>
+      <c r="E23" s="2" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A21" s="1"/>
-      <c r="B21" s="1"/>
-      <c r="C21" s="1"/>
-      <c r="D21" s="1"/>
-      <c r="E21" s="2"/>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A24" s="1"/>
+      <c r="B24" s="1"/>
+      <c r="C24" s="1"/>
+      <c r="D24" s="1"/>
+      <c r="E24" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/grant_es.xlsx
+++ b/data/grant_es.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Documents\GitHub\Mile_CV\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95280B3B-6ACD-4F1E-AFF8-94AC3479C6DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ABB1D75A-22AC-4566-9F0F-C0E8277E0A16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="52">
   <si>
     <t>what</t>
   </si>
@@ -113,9 +113,6 @@
   </si>
   <si>
     <t>Proyecto: Efecto de la disponibilidad de recursos sobre las preferencias de las mujeres por la masculinidad de los rostros en interacción con factores hormonales, cognitivos, y socio-contextuales como la escasez de recursos real y la exposición a violencias: un estudio experimental usando eye-tracking</t>
-  </si>
-  <si>
-    <t>IX \href{https://www.unbosque.edu.co/centro-informacion/convocatoria/xiv-convocatoria-interna-de-investigaciones}{Convocatoria Interna para la Financiación de Proyectos de Investigación}, 2024</t>
   </si>
   <si>
     <t>Ene. 2024 - Ene. 2026</t>
@@ -162,6 +159,24 @@
   </si>
   <si>
     <t>Role: Coinvestigadora</t>
+  </si>
+  <si>
+    <t>Role: Co-researcher</t>
+  </si>
+  <si>
+    <t>COP\$635.000.000</t>
+  </si>
+  <si>
+    <t>Proyecto: Funciones evolutivas del habla dirigida a bebés: Impacto en la atención, las preferencias auditivas y el desarrollo lingüístico y musical temprano</t>
+  </si>
+  <si>
+    <t>Feb. 2026 - Presente</t>
+  </si>
+  <si>
+    <t>IX \href{https://www.unbosque.edu.co/centro-informacion/convocatoria/xiv-convocatoria-interna-de-investigaciones}{IX Convocatoria Interna para la Financiación de Proyectos de Investigación}, 2024</t>
+  </si>
+  <si>
+    <t>XV \href{https://github.com/JDLeongomez/Proyecto-IDS}{XV Convocatoria Interna para la Financiación de Proyectos de Investigación}, 2025</t>
   </si>
 </sst>
 </file>
@@ -1011,7 +1026,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E24"/>
+  <dimension ref="A1:E27"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="75" bestFit="1" customWidth="1"/>
@@ -1038,21 +1053,21 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="72" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>42</v>
+        <v>9</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>43</v>
+        <v>5</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
@@ -1070,24 +1085,24 @@
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
       <c r="E4" s="2" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="72" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="E5" s="1" t="s">
         <v>44</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A5" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
@@ -1096,7 +1111,7 @@
       <c r="C6" s="1"/>
       <c r="D6" s="1"/>
       <c r="E6" s="1" t="s">
-        <v>22</v>
+        <v>45</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
@@ -1105,24 +1120,24 @@
       <c r="C7" s="1"/>
       <c r="D7" s="1"/>
       <c r="E7" s="2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>28</v>
+        <v>5</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
@@ -1130,60 +1145,60 @@
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
       <c r="D9" s="1"/>
-      <c r="E9" s="2" t="s">
+      <c r="E9" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A10" s="1"/>
+      <c r="B10" s="1"/>
+      <c r="C10" s="1"/>
+      <c r="D10" s="1"/>
+      <c r="E10" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A11" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A12" s="1"/>
+      <c r="B12" s="1"/>
+      <c r="C12" s="1"/>
+      <c r="D12" s="1"/>
+      <c r="E12" s="2" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A10" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="B10" s="1" t="s">
+    <row r="13" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A13" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B13" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="C10" s="1" t="s">
+      <c r="C13" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D10" s="1" t="s">
+      <c r="D13" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="E10" s="1" t="s">
+      <c r="E13" s="1" t="s">
         <v>26</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A11" s="1"/>
-      <c r="B11" s="1"/>
-      <c r="C11" s="1"/>
-      <c r="D11" s="1"/>
-      <c r="E11" s="2" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A12" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A13" s="1"/>
-      <c r="B13" s="1"/>
-      <c r="C13" s="1"/>
-      <c r="D13" s="1"/>
-      <c r="E13" s="1" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
@@ -1192,24 +1207,24 @@
       <c r="C14" s="1"/>
       <c r="D14" s="1"/>
       <c r="E14" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D15" s="1" t="s">
         <v>5</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>8</v>
+        <v>37</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
@@ -1218,7 +1233,7 @@
       <c r="C16" s="1"/>
       <c r="D16" s="1"/>
       <c r="E16" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.3">
@@ -1227,15 +1242,15 @@
       <c r="C17" s="1"/>
       <c r="D17" s="1"/>
       <c r="E17" s="2" t="s">
-        <v>11</v>
+        <v>24</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>9</v>
@@ -1243,8 +1258,8 @@
       <c r="D18" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="E18" s="2" t="s">
-        <v>39</v>
+      <c r="E18" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.3">
@@ -1253,7 +1268,7 @@
       <c r="C19" s="1"/>
       <c r="D19" s="1"/>
       <c r="E19" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.3">
@@ -1262,24 +1277,24 @@
       <c r="C20" s="1"/>
       <c r="D20" s="1"/>
       <c r="E20" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" ht="72" x14ac:dyDescent="0.3">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E21" s="1" t="s">
-        <v>19</v>
+        <v>5</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.3">
@@ -1297,15 +1312,50 @@
       <c r="C23" s="1"/>
       <c r="D23" s="1"/>
       <c r="E23" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" ht="72" x14ac:dyDescent="0.3">
+      <c r="A24" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A25" s="1"/>
+      <c r="B25" s="1"/>
+      <c r="C25" s="1"/>
+      <c r="D25" s="1"/>
+      <c r="E25" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A26" s="1"/>
+      <c r="B26" s="1"/>
+      <c r="C26" s="1"/>
+      <c r="D26" s="1"/>
+      <c r="E26" s="2" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A24" s="1"/>
-      <c r="B24" s="1"/>
-      <c r="C24" s="1"/>
-      <c r="D24" s="1"/>
-      <c r="E24" s="2"/>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A27" s="1"/>
+      <c r="B27" s="1"/>
+      <c r="C27" s="1"/>
+      <c r="D27" s="1"/>
+      <c r="E27" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
